--- a/output/pdf_financials_xlsx/BHS.xlsx
+++ b/output/pdf_financials_xlsx/BHS.xlsx
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.276171</v>
+        <v>-1.276171</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-2.276627</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.575022</v>
+        <v>-0.575022</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.07121</v>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.276171</v>
+        <v>-1.276171</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-2.276627</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.575022</v>
+        <v>-0.575022</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.07121</v>
@@ -1767,13 +1767,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.276171</v>
+        <v>-1.276171</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-2.276627</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.575022</v>
+        <v>-0.575022</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.07121</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-31.904275</v>
+        <v>31.904275</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>45.53254</v>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.276171</v>
+        <v>-1.276171</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-2.276627</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.575022</v>
+        <v>-0.575022</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.07121</v>
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.276171</v>
+        <v>-1.276171</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-2.276627</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.575022</v>
+        <v>-0.575022</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.07121</v>
@@ -2273,13 +2273,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -5917,22 +5917,22 @@
         <v>6.667413</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.661447</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>10.653542</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>11.637428</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>12.39117</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>14.437424</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>18.295018</v>
       </c>
     </row>
     <row r="93">
@@ -10139,7 +10139,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11143,7 +11147,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11842,7 +11850,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -14188,7 +14200,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -15067,7 +15083,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -76960,10 +76980,10 @@
         </is>
       </c>
       <c r="E689" s="5" t="n">
-        <v>1.276171</v>
+        <v>-1.276171</v>
       </c>
       <c r="F689" s="5" t="n">
-        <v>2.276627</v>
+        <v>-2.276627</v>
       </c>
       <c r="G689" t="inlineStr">
         <is>
@@ -81965,10 +81985,10 @@
         </is>
       </c>
       <c r="J739" s="5" t="n">
-        <v>0.893756</v>
+        <v>-0.893756</v>
       </c>
       <c r="K739" s="5" t="n">
-        <v>0.776529</v>
+        <v>-0.776529</v>
       </c>
       <c r="L739" t="inlineStr">
         <is>
@@ -83562,16 +83582,16 @@
         </is>
       </c>
       <c r="G755" s="5" t="n">
-        <v>0.575022</v>
+        <v>-0.575022</v>
       </c>
       <c r="H755" s="5" t="n">
-        <v>0.61775</v>
+        <v>-0.61775</v>
       </c>
       <c r="I755" s="5" t="n">
-        <v>0.948357</v>
+        <v>-0.948357</v>
       </c>
       <c r="J755" s="5" t="n">
-        <v>0.893756</v>
+        <v>-0.893756</v>
       </c>
       <c r="K755" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BHS.xlsx
+++ b/output/pdf_financials_xlsx/BHS.xlsx
@@ -2436,49 +2436,49 @@
         <v>0.558772</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.558772</v>
+        <v>0.00724</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000632</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.003682</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000385</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.009698999999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.053978</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.0418</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.06865300000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.026374</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.432062</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.310442</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.482566</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.56813</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.431804</v>
       </c>
     </row>
     <row r="35">
@@ -2552,49 +2552,49 @@
         <v>0.558772</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.558772</v>
+        <v>0.00724</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000632</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.003682</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000385</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.009698999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.053978</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.0418</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.06865300000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.026374</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.432062</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.310442</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.482566</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.56813</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.431804</v>
       </c>
     </row>
     <row r="37">
@@ -3248,49 +3248,49 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0</v>
+        <v>0.008593999999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.015169</v>
+        <v>0.014537</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.257708</v>
+        <v>1.254026</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.68538</v>
+        <v>1.684995</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.08748599999999999</v>
+        <v>0.077787</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.233091</v>
+        <v>0.179113</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.25732</v>
+        <v>0.21552</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.582584</v>
+        <v>0.513931</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.433569</v>
+        <v>0.407195</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.138444</v>
+        <v>0.706382</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.800767</v>
+        <v>0.490325</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.02773</v>
+        <v>0.545164</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.255033</v>
+        <v>0.686903</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.167057</v>
+        <v>0.735253</v>
       </c>
     </row>
     <row r="49">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -18509,7 +18509,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">

--- a/output/pdf_financials_xlsx/BHS.xlsx
+++ b/output/pdf_financials_xlsx/BHS.xlsx
@@ -777,7 +777,7 @@
         <v>0.256835</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.285165</v>
+        <v>0.286011</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.283679</v>
@@ -1381,16 +1381,16 @@
         <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.022004</v>
+        <v>-0.022004</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.052996</v>
+        <v>-0.052996</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.096566</v>
+        <v>-0.096566</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.027666</v>
+        <v>-0.027666</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -6361,22 +6361,22 @@
         <v>-0.062067</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.003236</v>
+        <v>0.015356</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.003236</v>
+        <v>0.010476</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.011625</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.010132</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004712</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005573</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>0.008262</v>
@@ -6666,7 +6666,7 @@
         <v>-0.882985</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.079211</v>
+        <v>0.073638</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>0.267245</v>
@@ -6965,25 +6965,25 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.09732</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.293207</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.678967</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.071203</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.022612</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.026892</v>
       </c>
     </row>
     <row r="112">
@@ -8343,25 +8343,25 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.09732</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.293207</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.678967</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.071203</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.022612</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.026892</v>
       </c>
     </row>
     <row r="135">
@@ -8409,25 +8409,25 @@
         <v>-2.782709</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.37406</v>
+        <v>-1.47138</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-2.108991</v>
+        <v>-2.402198</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-3.829437</v>
+        <v>-4.508404</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.922469</v>
+        <v>-1.993672</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-0.633212</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-1.250136</v>
+        <v>-1.272748</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-2.106719</v>
+        <v>-2.133611</v>
       </c>
     </row>
   </sheetData>
@@ -27432,7 +27432,11 @@
           <t>Acquisition of equipment 4</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -27832,7 +27836,11 @@
           <t>Gross proceeds from share issuance 6</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -31475,7 +31483,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -31669,7 +31681,11 @@
           <t>Gross proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -32322,7 +32338,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -34700,7 +34720,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -35201,7 +35225,11 @@
           <t>Shares issued for cash 8(b) 18,465,000 1,353,741 560,634</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -36215,7 +36243,11 @@
           <t>Shares issued for cash 8(b) 32,869,895 1,824,608 660,416</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -37518,7 +37550,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -39377,7 +39413,11 @@
           <t>Shares issued for cash 8 (b) 18,465,000 1,353,741 560,634</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -40490,7 +40530,11 @@
           <t>Shares issued for cash 8 (b) 12,705,608 1,455,565 549,445</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -42284,7 +42328,11 @@
           <t>Shares issued for cash 8 (b) 12,705,608 1,455,565 549,445</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -43700,7 +43748,11 @@
           <t>Shares issued for cash 8 (b) 7,500,000 881,693 318,307</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -45108,7 +45160,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -51356,7 +51412,11 @@
           <t>GST receivables 6</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -56796,7 +56856,11 @@
           <t>GST receivable 6</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>-</t>
@@ -58507,7 +58571,11 @@
           <t>HST/GST receivable</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
           <t>-</t>
@@ -63141,7 +63209,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
@@ -72472,7 +72544,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
           <t>-</t>
@@ -73943,7 +74019,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr"/>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E658" t="inlineStr">
         <is>
           <t>-</t>
@@ -75295,7 +75375,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E672" t="inlineStr">
         <is>
           <t>-</t>
@@ -86788,7 +86872,11 @@
           <t>Directors’ fees (Note 7)</t>
         </is>
       </c>
-      <c r="D787" t="inlineStr"/>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E787" t="inlineStr">
         <is>
           <t>-</t>
